--- a/target/diffStockItems.xlsx
+++ b/target/diffStockItems.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WG1623105038 WG9716943010</t>
+          <t>WG9716943010</t>
         </is>
       </c>
     </row>
@@ -591,17 +591,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WG9116316033 752W06100-0001 WG9716943010</t>
+          <t>WG9725472075 AZ992555200011 WG9925810001 WG9925810002</t>
         </is>
       </c>
     </row>
@@ -611,17 +611,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WG9716943010</t>
+          <t>810W62550-0011 810W62550-0012 AZ992555200011 WG9925810001 WG9925810002</t>
         </is>
       </c>
     </row>
@@ -631,17 +631,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AZ992555200011</t>
+          <t>WG9918588017 WG9918588018 WG9716943010 WG9925810001 WG9925810002</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WG9725472075 AZ992555200011 WG9925810001 WG9925810002</t>
+          <t>WG9716943010</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>WG9918588017 WG9918588018 WG9716943010 WG9925810001 WG9925810002</t>
+          <t>WG9116316033 711W61900-7132 AZ166482001032 810W62550-0011 810W62550-0012 WG9925810001 WG9925810002</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WG9716943010</t>
+          <t>752W41615-5015 752W41615-5015 850W41720-5025 AZ992555500029 811W41722-6022 811W41722-6022 810W26400-6353 712W28230-0007 810W26430-6068 WG9000360714 WG9000360714</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>810W62550-0011 810W62550-0012 AZ992555200011 WG9925810001 WG9925810002</t>
+          <t>850W41720-5025 WG9116316033 AZ9X25939527 811W41722-6022 810W26400-6353 810W26400-6353 810W26430-6068 810W26440-0063 711W61900-7134 WG9000360782 WG9000360782 YG9725190070 WG9925860020</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WG9116316033 711W61900-7132 AZ166482001032 WG9918588091 810W62550-0011 810W62550-0012 WG9925810001 WG9925810002</t>
+          <t>752W41615-5015 752W41615-5015 752W41615-5016 WG9731520059 850W41720-5025 WG9931470260 AZ992555500029 YZ952536000197 811W41722-6022 712W28230-0007 WG9000360714 YZ952555000148 YZ160082120020 811W41722-6032 811W41722-6032 WG9X25190066 WG9X25190066 YG9725190064 WG9925860020 712W97420-0002</t>
         </is>
       </c>
     </row>
@@ -771,77 +771,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>752W41615-5015 752W41615-5015 752W41615-5016 752W41615-5016 850W41720-5025 AZ992555500029 811W41722-6022 811W41722-6022 810W26400-6353 712W28230-0007 810W26430-6068 752W51715-0024 WG9000360714 WG9000360714 WG9725543351</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2023-11-09</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>850W41720-5025 WG9116316033 AZ9X25939527 811W41722-6022 810W26400-6353 810W26400-6353 810W26430-6068 810W26440-0063 711W61900-7134 WG9000360782 WG9000360782 YG9725190070 WG9100360787 WG9925860020</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>752W41615-5015 752W41615-5016 WG9731520059 850W41720-5025 WG9931470260 AZ992555500029 YZ952536000197 811W41722-6022 712W28230-0007 WG9000360714 YZ952555000148 YZ160082120020 811W41722-6032 811W41722-6032 WG9X25190066 WG9X25190066 YG9725190064 WG9925860020 712W97420-0002 WG9725543351</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>WG9750680075 WG9750680075 850W41720-5025 YG9725684105 WG9925682111 WG9325550560 WG9325550560 WG9925682111 WG9925682111 YZ16D269000031 811W41722-6022 850W41720-5025 811W41722-6022 811W41722-6022 711W61900-7134 752W51715-0024 WG9000360782 811W41722-6032 YG9725190064 YG9725190070 752W51715-0024 WG9000360782 752W41615-5101 752W41615-5107 752W41615-5107 811W25101-6017 811W25101-6018 712W42940-4039 WG9925860020 WG9325590220 WG9325590220 YG9325590224</t>
+          <t>850W41720-5025 YG9725684105 WG9925682111 WG9925682111 WG9925682111 YZ16D269000031 811W41722-6022 850W41720-5025 811W41722-6022 811W41722-6022 711W61900-7134 WG9000360782 811W41722-6032 YG9725190064 YG9725190070 WG9000360782 752W41615-5101 752W41615-5107 752W41615-5107 811W25101-6017 811W25101-6018 712W42940-4039 WG9925860020 WG9325590220 WG9325590220 YG9325590224</t>
         </is>
       </c>
     </row>

--- a/target/diffStockItems.xlsx
+++ b/target/diffStockItems.xlsx
@@ -451,17 +451,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WG9925810001 WG9925810002</t>
+          <t>WG9116316033 810W26400-6353 810W26400-6353 810W26430-6068</t>
         </is>
       </c>
     </row>
@@ -471,17 +471,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WG1664330061 WG9716943010</t>
+          <t>WG9725472075</t>
         </is>
       </c>
     </row>
@@ -491,17 +491,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WG9416520011 WG9416520012 AZ16D471000003</t>
+          <t>WG9725472075 810W62550-0011 810W62550-0012 AZ991858800120 WG9925810001 WG9925810002</t>
         </is>
       </c>
     </row>
@@ -511,17 +511,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WG9725472075 WG9116316033 WG9925810001 WG9925810002</t>
+          <t>810W62550-0011 810W62550-0012 WG9925810001 WG9925810002</t>
         </is>
       </c>
     </row>
@@ -531,17 +531,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WG9925810001 WG9925810002</t>
+          <t>WG9116316033 810W62550-0011 810W62550-0012 WG9925810001 WG9925810002</t>
         </is>
       </c>
     </row>
@@ -551,17 +551,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WG1623105038 WG9716943010</t>
+          <t>WG9725472075 WG9925810001 WG9925810002</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WG9716943010</t>
+          <t>WG9116316033 712W42940-4031</t>
         </is>
       </c>
     </row>
@@ -591,17 +591,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WG9725472075 AZ992555200011 WG9925810001 WG9925810002</t>
+          <t>WG9725472075 810W62550-0011 810W62550-0012 AZ9918270211 WG9925810001 WG9925810002</t>
         </is>
       </c>
     </row>
@@ -611,17 +611,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>810W62550-0011 810W62550-0012 AZ992555200011 WG9925810001 WG9925810002</t>
+          <t>WG9925930627 AZ992576000003</t>
         </is>
       </c>
     </row>
@@ -631,17 +631,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WG9918588017 WG9918588018 WG9716943010 WG9925810001 WG9925810002</t>
+          <t>810W62550-0011 810W62550-0012 WG9925810001 WG9925810002 WG9925551743</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WG9716943010</t>
+          <t>WG9725472075 YG9725524102 712W25441-5343 712W25441-5343 WG9925192114 YZ900036150022 WG9925810001 WG9925810002 WG9925551743</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>810W62550-0011 810W62550-0012 AZ992555200011 WG9925810001 WG9925810002</t>
+          <t>YZ962582000010 WG9725472075 712W25441-5343 712W66420-8154 712W66420-8154 810W62910-5299 810W62550-0011 810W62550-0012 712W63730-6573 712-32620-000028 YZ900036150022 WG9925810001 WG9925810002 WG9925551743 WG9925551743</t>
         </is>
       </c>
     </row>
@@ -691,17 +691,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>WG9116316033 711W61900-7132 AZ166482001032 810W62550-0011 810W62550-0012 WG9925810001 WG9925810002</t>
+          <t>WG9116316033 712W66420-8154 AZ936093006070 YZ962582000010 810W62910-5299 810W62550-0011 810W62550-0012 712W63730-6573 712W06340-0027 YZ900036150022 AZ160023000122 AZ160023000123 AZ166423700005 AZ160084000018 AZ992511200004 WG9925810001 WG9925810002 AZ000077000209</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>752W41615-5015 752W41615-5015 850W41720-5025 AZ992555500029 811W41722-6022 811W41722-6022 810W26400-6353 712W28230-0007 810W26430-6068 WG9000360714 WG9000360714</t>
+          <t>WG9925688220 YZ962582000010 712W66420-8154 810W41701-0076 WG9925550060 810W62910-5299 810W62550-0011 810W62550-0012 712W25441-5342 712W63730-6573 812W63730-6656 WG9918788104 711W61900-7130 712W06340-0027 YZ952553000698 YZ900036150022 YZ167182300156 WG9718360070 WG9925810001 WG9925810002 YZ952555000148 WG9925551743 YZ952577400003 712W97420-0011 810-41715-6016 WG9918788101</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>850W41720-5025 WG9116316033 AZ9X25939527 811W41722-6022 810W26400-6353 810W26400-6353 810W26430-6068 810W26440-0063 711W61900-7134 WG9000360782 WG9000360782 YG9725190070 WG9925860020</t>
+          <t>WG9925528030 WG9925688220 WG9925688221 WG9925550060 WG9925823020 712W66420-8154 AZ9X2593000055 810W41701-0076 AZ000068000013 WG9925682204 WG9925688220 WG9925688221 WG9925550060 WG9925688220 WG9925688221 YZ962582000010 YZ962582000010 810W62910-5298 810W62910-5299 810W62550-0011 810W62550-0012 WG1662579001 712W63730-6573 AZ991858800120 812W63730-6656 712W25441-5342 WG9918788104 WG9925530518 711W61900-7130 711W61900-7132 AZ992576000021 712W06340-0027 AZ020093000044 YZ900036150022 712W97420-0011 AZ160023000122 AZ160023000123 AZ166423700005 WG9X25190065 WG9718360070 YZ900036150022 YZ900036150025 AZ9918270211 WG9925810001 WG9925810002 WG9925551743 WG9925551743 712W97420-0011 712W97420-0011 810-41715-6016 WG9918788101</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>752W41615-5015 752W41615-5015 752W41615-5016 WG9731520059 850W41720-5025 WG9931470260 AZ992555500029 YZ952536000197 811W41722-6022 712W28230-0007 WG9000360714 YZ952555000148 YZ160082120020 811W41722-6032 811W41722-6032 WG9X25190066 WG9X25190066 YG9725190064 WG9925860020 712W97420-0002</t>
+          <t>WG9725523514 WG9925526001 WG9925526006 WG9925526007 WG9925526011 WG9925526016 WG9925526017 WG9925526019 WG9925526021 WG9925526023 WG9925526024 WG9925526030 WG9925526031 WG9925526032 WG9925526033 WG9925526034 WG9925686004 752W41210-0329 WG9416520011 WG9416520012 YG1671690022 712W25441-5342 WG9X25190065 712W63730-6573 712W25441-5342 AZ16D471000003 812W63730-6656 WG9918788104 YZ952553000698 YZ900036150022 YZ167182300156 712W97420-0011</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>850W41720-5025 YG9725684105 WG9925682111 WG9925682111 WG9925682111 YZ16D269000031 811W41722-6022 850W41720-5025 811W41722-6022 811W41722-6022 711W61900-7134 WG9000360782 811W41722-6032 YG9725190064 YG9725190070 WG9000360782 752W41615-5101 752W41615-5107 752W41615-5107 811W25101-6017 811W25101-6018 712W42940-4039 WG9925860020 WG9325590220 WG9325590220 YG9325590224</t>
+          <t>WG9925528030 WG9925688220 WG9925688221 WG9925688101 YG9725524102 712W66420-8154 810W41701-0076 YG9725684105 YG9925688409 WG9925688101 WG9925688101 WG9925550060 WG9925688101 YZ962582000010 810W62910-5298 810W62910-5299 810W62550-0011 810W62550-0012 712W63730-6573 812W63730-6656 712W25441-5342 AZ16D474000063 AZ16D474000068 WG9918788104 711W61900-7130 712W06340-0027 YZ900036150022 WG9X25190065 WG9718360070 WG9925810001 WG9925810002 WG9925551743 712W97420-0011 712W97420-0011 712W97420-0011 810-41715-6016 WG9918788101 WG9925550060</t>
         </is>
       </c>
     </row>
